--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3568,10 +3568,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830279</v>
+        <v>119830277</v>
       </c>
       <c r="B27" t="n">
-        <v>57744</v>
+        <v>57679</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,37 +3580,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830277</v>
+        <v>119830279</v>
       </c>
       <c r="B28" t="n">
-        <v>57679</v>
+        <v>57744</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3704,37 +3704,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3058,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830419</v>
+        <v>119830277</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>57679</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,37 +3074,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3114,13 +3110,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>411368</v>
+        <v>411307</v>
       </c>
       <c r="R23" t="n">
-        <v>6765989</v>
+        <v>6766061</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,12 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119829827</v>
+        <v>119830419</v>
       </c>
       <c r="B24" t="n">
-        <v>57986</v>
+        <v>56522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,21 +3198,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3230,7 +3221,11 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -3239,17 +3234,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410904</v>
+        <v>411368</v>
       </c>
       <c r="R24" t="n">
-        <v>6765884</v>
+        <v>6765989</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3268,7 +3263,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3278,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3283,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,10 +3315,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830001</v>
+        <v>119830279</v>
       </c>
       <c r="B25" t="n">
-        <v>58017</v>
+        <v>57744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,21 +3331,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103057</v>
+        <v>102999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3357,7 +3357,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411242</v>
+        <v>411307</v>
       </c>
       <c r="R25" t="n">
-        <v>6765895</v>
+        <v>6766061</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119829798</v>
+        <v>119830000</v>
       </c>
       <c r="B26" t="n">
-        <v>56514</v>
+        <v>57953</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,20 +3451,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>103042</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3481,23 +3481,23 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410888</v>
+        <v>411242</v>
       </c>
       <c r="R26" t="n">
-        <v>6765890</v>
+        <v>6765895</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,12 +3536,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Flög upp framför mig.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3568,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830277</v>
+        <v>119829798</v>
       </c>
       <c r="B27" t="n">
-        <v>57679</v>
+        <v>56514</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,20 +3575,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3603,30 +3598,30 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411307</v>
+        <v>410888</v>
       </c>
       <c r="R27" t="n">
-        <v>6766061</v>
+        <v>6765890</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3640,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3655,7 +3650,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3665,7 +3660,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Flög upp framför mig.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830279</v>
+        <v>119830001</v>
       </c>
       <c r="B28" t="n">
-        <v>57744</v>
+        <v>58017</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102999</v>
+        <v>103057</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3734,7 +3734,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411307</v>
+        <v>411242</v>
       </c>
       <c r="R28" t="n">
-        <v>6766061</v>
+        <v>6765895</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3816,10 +3816,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830000</v>
+        <v>119829827</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>57986</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3864,17 +3864,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411242</v>
+        <v>410904</v>
       </c>
       <c r="R29" t="n">
-        <v>6765895</v>
+        <v>6765884</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -2934,7 +2934,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830056</v>
+        <v>119830277</v>
       </c>
       <c r="B22" t="n">
         <v>57679</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411274</v>
+        <v>411307</v>
       </c>
       <c r="R22" t="n">
-        <v>6765999</v>
+        <v>6766061</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830277</v>
+        <v>119830279</v>
       </c>
       <c r="B23" t="n">
-        <v>57679</v>
+        <v>57744</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,37 +3070,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830419</v>
+        <v>119830056</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>57679</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,21 +3198,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3221,14 +3221,10 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3238,13 +3234,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411368</v>
+        <v>411274</v>
       </c>
       <c r="R24" t="n">
-        <v>6765989</v>
+        <v>6765999</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3273,7 +3269,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,12 +3279,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,10 +3306,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830279</v>
+        <v>119829827</v>
       </c>
       <c r="B25" t="n">
-        <v>57744</v>
+        <v>57986</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3327,25 +3318,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3357,23 +3348,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411307</v>
+        <v>410904</v>
       </c>
       <c r="R25" t="n">
-        <v>6766061</v>
+        <v>6765884</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3392,7 +3383,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3402,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830000</v>
+        <v>119830001</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>58017</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,20 +3442,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103042</v>
+        <v>103057</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3481,7 +3472,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3563,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119829798</v>
+        <v>119830419</v>
       </c>
       <c r="B27" t="n">
-        <v>56514</v>
+        <v>56522</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,25 +3566,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3602,26 +3593,30 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410888</v>
+        <v>411368</v>
       </c>
       <c r="R27" t="n">
-        <v>6765890</v>
+        <v>6765989</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3635,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3650,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3660,12 +3655,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flög upp framför mig.</t>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,10 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830001</v>
+        <v>119829798</v>
       </c>
       <c r="B28" t="n">
-        <v>58017</v>
+        <v>56514</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3708,16 +3703,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103057</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3734,23 +3729,23 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411242</v>
+        <v>410888</v>
       </c>
       <c r="R28" t="n">
-        <v>6765895</v>
+        <v>6765890</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3769,7 +3764,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3779,7 +3774,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3784,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flög upp framför mig.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3816,10 +3816,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119829827</v>
+        <v>119830000</v>
       </c>
       <c r="B29" t="n">
-        <v>57986</v>
+        <v>57953</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3864,17 +3864,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410904</v>
+        <v>411242</v>
       </c>
       <c r="R29" t="n">
-        <v>6765884</v>
+        <v>6765895</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -2934,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830277</v>
+        <v>119830000</v>
       </c>
       <c r="B22" t="n">
-        <v>57679</v>
+        <v>57953</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,20 +2946,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2986,13 +2986,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411307</v>
+        <v>411242</v>
       </c>
       <c r="R22" t="n">
-        <v>6766061</v>
+        <v>6765895</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830279</v>
+        <v>119830277</v>
       </c>
       <c r="B23" t="n">
-        <v>57744</v>
+        <v>57679</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,37 +3070,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830056</v>
+        <v>119829827</v>
       </c>
       <c r="B24" t="n">
-        <v>57679</v>
+        <v>57986</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,16 +3198,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3224,23 +3224,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411274</v>
+        <v>410904</v>
       </c>
       <c r="R24" t="n">
-        <v>6765999</v>
+        <v>6765884</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3306,10 +3306,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119829827</v>
+        <v>119829798</v>
       </c>
       <c r="B25" t="n">
-        <v>57986</v>
+        <v>56514</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3318,20 +3318,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3348,7 +3348,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410904</v>
+        <v>410888</v>
       </c>
       <c r="R25" t="n">
-        <v>6765884</v>
+        <v>6765890</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,7 +3403,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flög upp framför mig.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830001</v>
+        <v>119830279</v>
       </c>
       <c r="B26" t="n">
-        <v>58017</v>
+        <v>57744</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103057</v>
+        <v>102999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3472,7 +3477,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3482,13 +3487,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411242</v>
+        <v>411307</v>
       </c>
       <c r="R26" t="n">
-        <v>6765895</v>
+        <v>6766061</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3517,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,7 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830419</v>
+        <v>119830001</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
+        <v>58017</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,25 +3571,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>103057</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3593,14 +3598,10 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3610,13 +3611,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411368</v>
+        <v>411242</v>
       </c>
       <c r="R27" t="n">
-        <v>6765989</v>
+        <v>6765895</v>
       </c>
       <c r="S27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3646,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,12 +3656,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3687,10 +3683,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119829798</v>
+        <v>119830056</v>
       </c>
       <c r="B28" t="n">
-        <v>56514</v>
+        <v>57679</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,20 +3695,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3729,23 +3725,23 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410888</v>
+        <v>411274</v>
       </c>
       <c r="R28" t="n">
-        <v>6765890</v>
+        <v>6765999</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3764,7 +3760,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3774,7 +3770,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3784,12 +3780,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flög upp framför mig.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3816,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830000</v>
+        <v>119830419</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>56522</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,25 +3819,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103042</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3855,7 +3846,11 @@
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -3868,13 +3863,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411242</v>
+        <v>411368</v>
       </c>
       <c r="R29" t="n">
-        <v>6765895</v>
+        <v>6765989</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3913,7 +3908,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -2934,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830000</v>
+        <v>119829827</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>57996</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,20 +2946,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2982,17 +2982,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411242</v>
+        <v>410904</v>
       </c>
       <c r="R22" t="n">
-        <v>6765895</v>
+        <v>6765884</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830277</v>
+        <v>119830000</v>
       </c>
       <c r="B23" t="n">
-        <v>57679</v>
+        <v>57963</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,20 +3070,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3093,14 +3093,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>411307</v>
+        <v>411242</v>
       </c>
       <c r="R23" t="n">
-        <v>6766061</v>
+        <v>6765895</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119829827</v>
+        <v>119830279</v>
       </c>
       <c r="B24" t="n">
-        <v>57986</v>
+        <v>57754</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3194,25 +3194,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3224,23 +3224,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410904</v>
+        <v>411307</v>
       </c>
       <c r="R24" t="n">
-        <v>6765884</v>
+        <v>6766061</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3306,10 +3306,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119829798</v>
+        <v>119830001</v>
       </c>
       <c r="B25" t="n">
-        <v>56514</v>
+        <v>58027</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3322,16 +3322,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>103057</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3348,23 +3348,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410888</v>
+        <v>411242</v>
       </c>
       <c r="R25" t="n">
-        <v>6765890</v>
+        <v>6765895</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3403,12 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flög upp framför mig.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830279</v>
+        <v>119830056</v>
       </c>
       <c r="B26" t="n">
-        <v>57744</v>
+        <v>57689</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3447,25 +3442,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3487,13 +3482,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411307</v>
+        <v>411274</v>
       </c>
       <c r="R26" t="n">
-        <v>6766061</v>
+        <v>6765999</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3522,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830001</v>
+        <v>119829798</v>
       </c>
       <c r="B27" t="n">
-        <v>58017</v>
+        <v>56524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,16 +3570,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103057</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3601,23 +3596,23 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411242</v>
+        <v>410888</v>
       </c>
       <c r="R27" t="n">
-        <v>6765895</v>
+        <v>6765890</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3636,7 +3631,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3646,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3656,7 +3651,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Flög upp framför mig.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,10 +3683,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830056</v>
+        <v>119830277</v>
       </c>
       <c r="B28" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3718,14 +3718,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3735,13 +3735,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411274</v>
+        <v>411307</v>
       </c>
       <c r="R28" t="n">
-        <v>6765999</v>
+        <v>6766061</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,7 +3810,7 @@
         <v>119830419</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -2934,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119829827</v>
+        <v>119830419</v>
       </c>
       <c r="B22" t="n">
-        <v>57996</v>
+        <v>56532</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2973,7 +2973,11 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>förbiflygande</t>
@@ -2982,17 +2986,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410904</v>
+        <v>411368</v>
       </c>
       <c r="R22" t="n">
-        <v>6765884</v>
+        <v>6765989</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3011,7 +3015,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3021,7 +3025,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3035,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3182,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119830279</v>
+        <v>119829798</v>
       </c>
       <c r="B24" t="n">
-        <v>57754</v>
+        <v>56524</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,21 +3207,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102999</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3224,23 +3233,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411307</v>
+        <v>410888</v>
       </c>
       <c r="R24" t="n">
-        <v>6766061</v>
+        <v>6765890</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3259,7 +3268,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3269,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3279,7 +3288,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flög upp framför mig.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830056</v>
+        <v>119829827</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57996</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,16 +3460,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3472,23 +3486,23 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411274</v>
+        <v>410904</v>
       </c>
       <c r="R26" t="n">
-        <v>6765999</v>
+        <v>6765884</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3507,7 +3521,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3517,7 +3531,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,7 +3541,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,10 +3568,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119829798</v>
+        <v>119830056</v>
       </c>
       <c r="B27" t="n">
-        <v>56524</v>
+        <v>57689</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,20 +3580,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3596,23 +3610,23 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410888</v>
+        <v>411274</v>
       </c>
       <c r="R27" t="n">
-        <v>6765890</v>
+        <v>6765999</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3645,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3641,7 +3655,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,12 +3665,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Flög upp framför mig.</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830277</v>
+        <v>119830279</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57754</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,37 +3704,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3770,7 +3779,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3780,7 +3789,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,10 +3816,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830419</v>
+        <v>119830277</v>
       </c>
       <c r="B29" t="n">
-        <v>56532</v>
+        <v>57689</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3823,37 +3832,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3863,13 +3868,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411368</v>
+        <v>411307</v>
       </c>
       <c r="R29" t="n">
-        <v>6765989</v>
+        <v>6766061</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3908,12 +3913,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -2934,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830419</v>
+        <v>119830277</v>
       </c>
       <c r="B22" t="n">
-        <v>56532</v>
+        <v>57689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,37 +2950,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2990,13 +2986,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411368</v>
+        <v>411307</v>
       </c>
       <c r="R22" t="n">
-        <v>6765989</v>
+        <v>6766061</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3035,12 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3067,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119830000</v>
+        <v>119830056</v>
       </c>
       <c r="B23" t="n">
-        <v>57963</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,20 +3070,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3109,7 +3100,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3119,13 +3110,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>411242</v>
+        <v>411274</v>
       </c>
       <c r="R23" t="n">
-        <v>6765895</v>
+        <v>6765999</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3154,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119829798</v>
+        <v>119830001</v>
       </c>
       <c r="B24" t="n">
-        <v>56524</v>
+        <v>58027</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,16 +3198,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>103057</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3233,23 +3224,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410888</v>
+        <v>411242</v>
       </c>
       <c r="R24" t="n">
-        <v>6765890</v>
+        <v>6765895</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3268,7 +3259,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3278,7 +3269,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,12 +3279,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:37</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flög upp framför mig.</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3306,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830001</v>
+        <v>119829827</v>
       </c>
       <c r="B25" t="n">
-        <v>58027</v>
+        <v>57996</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3332,20 +3318,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3362,23 +3348,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411242</v>
+        <v>410904</v>
       </c>
       <c r="R25" t="n">
-        <v>6765895</v>
+        <v>6765884</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3397,7 +3383,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3407,7 +3393,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3403,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119829827</v>
+        <v>119830279</v>
       </c>
       <c r="B26" t="n">
-        <v>57996</v>
+        <v>57754</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,25 +3442,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3486,23 +3472,23 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backholsbäcken, Dlr</t>
+          <t>Södra Trånggraven, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410904</v>
+        <v>411307</v>
       </c>
       <c r="R26" t="n">
-        <v>6765884</v>
+        <v>6766061</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,7 +3507,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3531,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3541,7 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3568,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830056</v>
+        <v>119830000</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57963</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,20 +3566,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3610,7 +3596,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3620,13 +3606,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411274</v>
+        <v>411242</v>
       </c>
       <c r="R27" t="n">
-        <v>6765999</v>
+        <v>6765895</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3655,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3665,7 +3651,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,10 +3678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830279</v>
+        <v>119830419</v>
       </c>
       <c r="B28" t="n">
-        <v>57754</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3704,20 +3690,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102999</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3731,10 +3717,14 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3744,13 +3734,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>411307</v>
+        <v>411368</v>
       </c>
       <c r="R28" t="n">
-        <v>6766061</v>
+        <v>6765989</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3779,7 +3769,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3779,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3816,10 +3811,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119830277</v>
+        <v>119829798</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>56524</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3828,20 +3823,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3851,30 +3846,30 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Trånggraven, Dlr</t>
+          <t>Backholsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411307</v>
+        <v>410888</v>
       </c>
       <c r="R29" t="n">
-        <v>6766061</v>
+        <v>6765890</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3893,7 +3888,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3903,7 +3898,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3913,7 +3908,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flög upp framför mig.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3938,6 +3938,409 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124820536</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Horrmundberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>410865</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6766135</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124820528</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Horrmundberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>410865</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6766135</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124820847</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>185</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Horrmundberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>411300</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6766064</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820536</v>
+        <v>124820528</v>
       </c>
       <c r="B30" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3956,21 +3956,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4076,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820528</v>
+        <v>124820847</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>78842</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,25 +4088,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R31" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4169,32 +4169,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4212,10 +4207,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B32" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4224,25 +4219,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R32" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4280,7 +4275,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4305,27 +4300,32 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820528</v>
+        <v>124820847</v>
       </c>
       <c r="B30" t="n">
-        <v>79920</v>
+        <v>78842</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R30" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4033,32 +4033,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4076,10 +4071,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,25 +4083,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R31" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4144,7 +4139,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4169,27 +4164,32 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820536</v>
+        <v>124820528</v>
       </c>
       <c r="B32" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4223,21 +4223,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B30" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R30" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4033,27 +4033,32 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4071,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820536</v>
+        <v>124820528</v>
       </c>
       <c r="B31" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4087,21 +4092,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4207,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820528</v>
+        <v>124820847</v>
       </c>
       <c r="B32" t="n">
-        <v>79920</v>
+        <v>78842</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4219,25 +4224,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R32" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4275,7 +4280,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4300,32 +4305,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820528</v>
+        <v>124820536</v>
       </c>
       <c r="B30" t="n">
-        <v>79920</v>
+        <v>79927</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3956,21 +3956,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820536</v>
+        <v>124820528</v>
       </c>
       <c r="B32" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4223,21 +4223,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820536</v>
+        <v>124820847</v>
       </c>
       <c r="B30" t="n">
-        <v>79927</v>
+        <v>78842</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R30" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4033,32 +4033,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4076,10 +4071,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,25 +4083,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R31" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4144,7 +4139,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4169,27 +4164,32 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B30" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R30" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4033,27 +4033,32 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4071,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820536</v>
+        <v>124820847</v>
       </c>
       <c r="B31" t="n">
-        <v>79927</v>
+        <v>78842</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4083,25 +4088,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R31" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4139,7 +4144,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4164,32 +4169,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -4076,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820847</v>
+        <v>124820528</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>79920</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,25 +4088,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R31" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4169,27 +4169,32 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4207,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820528</v>
+        <v>124820847</v>
       </c>
       <c r="B32" t="n">
-        <v>79920</v>
+        <v>78842</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4219,25 +4224,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R32" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4275,7 +4280,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4300,32 +4305,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820536</v>
+        <v>124820847</v>
       </c>
       <c r="B30" t="n">
-        <v>79927</v>
+        <v>78842</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R30" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4033,32 +4033,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4212,10 +4207,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B32" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4224,25 +4219,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R32" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4280,7 +4275,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4305,27 +4300,32 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124820847</v>
+        <v>124820536</v>
       </c>
       <c r="B30" t="n">
-        <v>78842</v>
+        <v>79927</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R30" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4033,27 +4033,32 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4207,10 +4212,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820536</v>
+        <v>124820847</v>
       </c>
       <c r="B32" t="n">
-        <v>79927</v>
+        <v>78842</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4219,25 +4224,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4250,10 +4255,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R32" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4275,7 +4280,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4300,32 +4305,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3943,7 +3943,7 @@
         <v>124820536</v>
       </c>
       <c r="B30" t="n">
-        <v>79927</v>
+        <v>80064</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4076,10 +4076,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124820528</v>
+        <v>124820847</v>
       </c>
       <c r="B31" t="n">
-        <v>79920</v>
+        <v>78979</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,25 +4088,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410865</v>
+        <v>411300</v>
       </c>
       <c r="R31" t="n">
-        <v>6766135</v>
+        <v>6766064</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Transtrand</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4169,32 +4169,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Ängsbarrskog</t>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>naturskog, måttligt dimensionsavverkad</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>trestammigt träd</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4212,10 +4207,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124820847</v>
+        <v>124820528</v>
       </c>
       <c r="B32" t="n">
-        <v>78842</v>
+        <v>80057</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4224,25 +4219,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4255,10 +4250,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411300</v>
+        <v>410865</v>
       </c>
       <c r="R32" t="n">
-        <v>6766064</v>
+        <v>6766135</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4280,7 +4275,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Transtrand</t>
+          <t>Lima</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4305,27 +4300,32 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>naturskog, måttligt dimensionsavverkad</t>
+          <t>Ängsbarrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>trestammigt träd</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # trestammigt träd</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -3945,11 +3945,6 @@
       <c r="B30" t="n">
         <v>80064</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>LC</t>
@@ -4081,11 +4076,6 @@
       <c r="B31" t="n">
         <v>78979</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4211,11 +4201,6 @@
       </c>
       <c r="B32" t="n">
         <v>80057</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4326,6 +4326,125 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126158376</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57755</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Södra Trånggraven, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>411355</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6765913</v>
+      </c>
+      <c r="S33" t="n">
+        <v>17</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -4331,7 +4331,7 @@
         <v>126158376</v>
       </c>
       <c r="B33" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -4331,7 +4331,7 @@
         <v>126158376</v>
       </c>
       <c r="B33" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 7383-2020 artfynd.xlsx
+++ b/artfynd/A 7383-2020 artfynd.xlsx
@@ -4331,7 +4331,7 @@
         <v>126158376</v>
       </c>
       <c r="B33" t="n">
-        <v>57760</v>
+        <v>57761</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
